--- a/first_sem/IIT/Lab_Report/marksheet.xlsx
+++ b/first_sem/IIT/Lab_Report/marksheet.xlsx
@@ -1,35 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pranish\Documents\GitHub\CSIT\first_sem\IIT\Lab_Report\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B1E09C4-790D-4229-8BA4-36AB96FE3C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="7"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{D02E4D6E-DCC4-45A2-8021-EBAABBE15EC7}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
@@ -38,83 +22,101 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
   <si>
-    <t>SN</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Subject</t>
-  </si>
-  <si>
-    <t>IIT</t>
-  </si>
-  <si>
-    <t>Digital Logic</t>
-  </si>
-  <si>
-    <t>Physic</t>
-  </si>
-  <si>
-    <t>TH</t>
-  </si>
-  <si>
-    <t>PR</t>
+    <t xml:space="preserve">SN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C Programming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital Logic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathematics-I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Obtained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Result</t>
   </si>
   <si>
     <t xml:space="preserve">TH </t>
   </si>
   <si>
-    <t>C Programming</t>
-  </si>
-  <si>
-    <t>Mathematics-I</t>
-  </si>
-  <si>
-    <t>Mark Obtained</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Percentage</t>
-  </si>
-  <si>
-    <t>Grade</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Suman Karki</t>
-  </si>
-  <si>
-    <t>Pratima Shrestha</t>
-  </si>
-  <si>
-    <t>Rojan Adhikari</t>
-  </si>
-  <si>
-    <t>Nisha Thapa</t>
-  </si>
-  <si>
-    <t>Gyani Ray</t>
-  </si>
-  <si>
-    <t>Bikash Gurung</t>
+    <t xml:space="preserve">PR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suman Karki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pratima Shrestha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rojan Adhikari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nisha Thapa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gyani Ray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bikash Gurung</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -126,68 +128,77 @@
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
@@ -216,28 +227,96 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Aptos Narrow"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF00B050"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -272,153 +351,55 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -426,33 +407,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -465,13 +437,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -481,15 +447,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -497,7 +461,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -505,66 +468,42 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85D6C0BF-2794-4EA8-AF35-B1CB072B5C60}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:Q9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5" customWidth="1"/>
-    <col min="4" max="4" width="4.5546875" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" customWidth="1"/>
-    <col min="6" max="6" width="6.88671875" customWidth="1"/>
-    <col min="7" max="7" width="5.33203125" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" customWidth="1"/>
-    <col min="9" max="9" width="4.88671875" customWidth="1"/>
-    <col min="10" max="10" width="4.5546875" customWidth="1"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1"/>
-    <col min="12" max="12" width="5.5546875" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.21875" bestFit="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="6.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="5.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="5.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="4.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="4.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="5.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11.22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -589,7 +528,7 @@
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
       <c r="B2" s="4"/>
       <c r="C2" s="2" t="s">
@@ -597,69 +536,69 @@
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
       <c r="B3" s="4"/>
       <c r="C3" s="3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -667,57 +606,57 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="M4" s="3">
-        <f>SUM(C4:L4)</f>
+      <c r="M4" s="3" t="n">
+        <f aca="false">SUM(C4:L4)</f>
         <v>399</v>
       </c>
-      <c r="N4" s="3">
-        <f>AVERAGE(C4:L4)</f>
+      <c r="N4" s="3" t="n">
+        <f aca="false">AVERAGE(C4:L4)</f>
         <v>39.9</v>
       </c>
-      <c r="O4" s="3">
-        <f>IF(OR(C4&lt;24,E4&lt;24,G4&lt;24,I4&lt;24,K4&lt;24),"NG",(M4/500)*100)</f>
-        <v>79.800000000000011</v>
+      <c r="O4" s="3" t="n">
+        <f aca="false">IF(OR(C4&lt;24,E4&lt;24,G4&lt;24,I4&lt;24,K4&lt;24),"NG",(M4/500)*100)</f>
+        <v>79.8</v>
       </c>
       <c r="P4" s="3" t="str">
-        <f>IF(O4="NG","NG",
+        <f aca="false">IF(O4="NG","NG",
 IF(O4&gt;=90,"A+",
 IF(O4&gt;=80,"A",
 IF(O4&gt;=70,"B+",
@@ -727,61 +666,61 @@
         <v>B+</v>
       </c>
       <c r="Q4" s="3" t="str">
-        <f>IF(O4="NG","Fail","Pass")</f>
+        <f aca="false">IF(O4="NG","Fail","Pass")</f>
         <v>Pass</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="M5" s="3">
-        <f t="shared" ref="M5:M9" si="0">SUM(C5:L5)</f>
+      <c r="M5" s="3" t="n">
+        <f aca="false">SUM(C5:L5)</f>
         <v>444</v>
       </c>
-      <c r="N5" s="3">
-        <f t="shared" ref="N5:N9" si="1">AVERAGE(C5:L5)</f>
+      <c r="N5" s="3" t="n">
+        <f aca="false">AVERAGE(C5:L5)</f>
         <v>44.4</v>
       </c>
-      <c r="O5" s="3">
-        <f t="shared" ref="O5:O9" si="2">IF(OR(C5&lt;24,E5&lt;24,G5&lt;24,I5&lt;24,K5&lt;24),"NG",(M5/500)*100)</f>
+      <c r="O5" s="3" t="n">
+        <f aca="false">IF(OR(C5&lt;24,E5&lt;24,G5&lt;24,I5&lt;24,K5&lt;24),"NG",(M5/500)*100)</f>
         <v>88.8</v>
       </c>
       <c r="P5" s="3" t="str">
-        <f t="shared" ref="P5:P9" si="3">IF(O5="NG","NG",
+        <f aca="false">IF(O5="NG","NG",
 IF(O5&gt;=90,"A+",
 IF(O5&gt;=80,"A",
 IF(O5&gt;=70,"B+",
@@ -791,322 +730,351 @@
         <v>A</v>
       </c>
       <c r="Q5" s="3" t="str">
-        <f t="shared" ref="Q5:Q9" si="4">IF(O5="NG","Fail","Pass")</f>
+        <f aca="false">IF(O5="NG","Fail","Pass")</f>
         <v>Pass</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M6" s="3">
-        <f t="shared" si="0"/>
+      <c r="M6" s="3" t="n">
+        <f aca="false">SUM(C6:L6)</f>
         <v>154</v>
       </c>
-      <c r="N6" s="3">
-        <f t="shared" si="1"/>
+      <c r="N6" s="3" t="n">
+        <f aca="false">AVERAGE(C6:L6)</f>
         <v>15.4</v>
       </c>
       <c r="O6" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f aca="false">IF(OR(C6&lt;24,E6&lt;24,G6&lt;24,I6&lt;24,K6&lt;24),"NG",(M6/500)*100)</f>
         <v>NG</v>
       </c>
       <c r="P6" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f aca="false">IF(O6="NG","NG",
+IF(O6&gt;=90,"A+",
+IF(O6&gt;=80,"A",
+IF(O6&gt;=70,"B+",
+IF(O6&gt;=60,"B",
+IF(O6&gt;=50,"C+",
+IF(O6&gt;=40,"C","NG")))))))</f>
         <v>NG</v>
       </c>
       <c r="Q6" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f aca="false">IF(O6="NG","Fail","Pass")</f>
         <v>Fail</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="M7" s="3">
-        <f t="shared" si="0"/>
+      <c r="M7" s="3" t="n">
+        <f aca="false">SUM(C7:L7)</f>
         <v>174</v>
       </c>
-      <c r="N7" s="3">
-        <f t="shared" si="1"/>
-        <v>17.399999999999999</v>
+      <c r="N7" s="3" t="n">
+        <f aca="false">AVERAGE(C7:L7)</f>
+        <v>17.4</v>
       </c>
       <c r="O7" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f aca="false">IF(OR(C7&lt;24,E7&lt;24,G7&lt;24,I7&lt;24,K7&lt;24),"NG",(M7/500)*100)</f>
         <v>NG</v>
       </c>
       <c r="P7" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f aca="false">IF(O7="NG","NG",
+IF(O7&gt;=90,"A+",
+IF(O7&gt;=80,"A",
+IF(O7&gt;=70,"B+",
+IF(O7&gt;=60,"B",
+IF(O7&gt;=50,"C+",
+IF(O7&gt;=40,"C","NG")))))))</f>
         <v>NG</v>
       </c>
       <c r="Q7" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f aca="false">IF(O7="NG","Fail","Pass")</f>
         <v>Fail</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="M8" s="3">
-        <f t="shared" si="0"/>
+      <c r="M8" s="3" t="n">
+        <f aca="false">SUM(C8:L8)</f>
         <v>466</v>
       </c>
-      <c r="N8" s="3">
-        <f t="shared" si="1"/>
+      <c r="N8" s="3" t="n">
+        <f aca="false">AVERAGE(C8:L8)</f>
         <v>46.6</v>
       </c>
-      <c r="O8" s="3">
-        <f t="shared" si="2"/>
+      <c r="O8" s="3" t="n">
+        <f aca="false">IF(OR(C8&lt;24,E8&lt;24,G8&lt;24,I8&lt;24,K8&lt;24),"NG",(M8/500)*100)</f>
         <v>93.2</v>
       </c>
       <c r="P8" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f aca="false">IF(O8="NG","NG",
+IF(O8&gt;=90,"A+",
+IF(O8&gt;=80,"A",
+IF(O8&gt;=70,"B+",
+IF(O8&gt;=60,"B",
+IF(O8&gt;=50,"C+",
+IF(O8&gt;=40,"C","NG")))))))</f>
         <v>A+</v>
       </c>
       <c r="Q8" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f aca="false">IF(O8="NG","Fail","Pass")</f>
         <v>Pass</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M9" s="3">
-        <f t="shared" si="0"/>
+      <c r="M9" s="3" t="n">
+        <f aca="false">SUM(C9:L9)</f>
         <v>190</v>
       </c>
-      <c r="N9" s="3">
-        <f t="shared" si="1"/>
+      <c r="N9" s="3" t="n">
+        <f aca="false">AVERAGE(C9:L9)</f>
         <v>19</v>
       </c>
       <c r="O9" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f aca="false">IF(OR(C9&lt;24,E9&lt;24,G9&lt;24,I9&lt;24,K9&lt;24),"NG",(M9/500)*100)</f>
         <v>NG</v>
       </c>
       <c r="P9" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f aca="false">IF(O9="NG","NG",
+IF(O9&gt;=90,"A+",
+IF(O9&gt;=80,"A",
+IF(O9&gt;=70,"B+",
+IF(O9&gt;=60,"B",
+IF(O9&gt;=50,"C+",
+IF(O9&gt;=40,"C","NG")))))))</f>
         <v>NG</v>
       </c>
       <c r="Q9" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f aca="false">IF(O9="NG","Fail","Pass")</f>
         <v>Fail</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="C1:L1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Q4">
-    <cfRule type="dataBar" priority="8">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3F7B3983-C768-4FE4-9373-AA3DF098C55A}</x14:id>
-        </ext>
-      </extLst>
+  <conditionalFormatting sqref="G12 C4:C9 E4:E9 G4:G9 I4:I9 K4:K9">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>24</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="9">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C9 E4:E9 G4:G9 I4:I9 K4:K9">
+    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>24</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q4:Q9">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>"FAIL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O4:P9">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>"NG"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>"NG"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O6">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFCFCFF"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O6">
-    <cfRule type="colorScale" priority="7">
+  <conditionalFormatting sqref="Q4">
+    <cfRule type="dataBar" priority="9">
+      <dataBar showValue="1" minLength="10" maxLength="90">
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{14E11EE8-D876-41E6-BD83-2D34E47AA0A7}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="colorScale" priority="10">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFCFCFF"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O4:P9">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"NG"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal">
-      <formula>"NG"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q4:Q9">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
-      <formula>"FAIL"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C9 E4:E9 G4:G9 I4:I9 K4:K9">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
-      <formula>24</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12 C4:C9 E4:E9 G4:G9 I4:I9 K4:K9">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
-      <formula>24</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3F7B3983-C768-4FE4-9373-AA3DF098C55A}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+          <x14:cfRule type="dataBar" id="{14E11EE8-D876-41E6-BD83-2D34E47AA0A7}">
+            <x14:dataBar minLength="10" maxLength="90" axisPosition="automatic" gradient="false">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
               <x14:negativeFillColor rgb="FFFF0000"/>
